--- a/forms/trg/Formulir_TRG_p-rg.xlsx
+++ b/forms/trg/Formulir_TRG_p-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B34)</f>
+        <f>COUNTA(Anggota!B5:B35)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F34)</f>
+        <f>COUNTA(Anggota!F5:F35)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nasri, S.Hut., M.Hut., IPM.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Forestry, Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Forest Conservation; Forest Ecology; Conservation Genetics</t>
+          <t>Phytopathology; Agricultural Mycology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +929,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>54795337200</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,22 +946,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Eirene Brugman, S.P., M.Sc.</t>
+          <t>Ir. Nasri, S.Hut., M.Hut., IPM.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Agriculture, Hasanuddin University</t>
+          <t>Faculty of Forestry, Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Plant Pathogenic Oomycetes; Plant Pathogen Population Genetics</t>
+          <t>Forest Conservation; Forest Ecology; Conservation Genetics</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Asman, S.P., M.P., Ph.D.</t>
+          <t>Eirene Brugman, S.P., M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Plant Pathology; Plant Disease Epidemiology</t>
+          <t>Plant Pathogenic Oomycetes; Plant Pathogen Population Genetics</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Ade Rosmana, DEA.</t>
+          <t>Asman, S.P., M.P., Ph.D.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Plant Pest and Disease; Soilborne Disease</t>
+          <t>Plant Pathology; Plant Disease Epidemiology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1057,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Thomas Jung</t>
+          <t>Prof. Dr. Ir. Ade Rosmana, DEA.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Phytophthora Research Center, Department of Forest Protection and Wildlife Management, Mendel University in Brno</t>
+          <t>Faculty of Agriculture, Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Plant pathology; Forest Pathology; Evolutionary Biology; Taxonomy</t>
+          <t>Plant Pest and Disease; Soilborne Disease</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,22 +1094,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Bruno Scanu</t>
+          <t>Prof. Thomas Jung</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University of Sassari, Sassari (UNISS)</t>
+          <t>Phytophthora Research Center, Department of Forest Protection and Wildlife Management, Mendel University in Brno</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Forest Pathology; Invasive species; Taxonomy; Evolutionary Biology</t>
+          <t>Plant pathology; Forest Pathology; Evolutionary Biology; Taxonomy</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,22 +1131,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. David Guest</t>
+          <t>Prof. Bruno Scanu</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Sydney Institute of Agriculture, School of Life and Environmental Sciences, The University of Sydney, Australia</t>
+          <t>University of Sassari, Sassari (UNISS)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Plant Pathology; Plant-Pathogen Interaction; Integrated Crop Management</t>
+          <t>Forest Pathology; Invasive species; Taxonomy; Evolutionary Biology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,22 +1168,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Andre Drenth</t>
+          <t>Prof. David Guest</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Centre for Horticultural Science &amp; Professorial Research Fellow and Centre Director, Queensland Alliance for Agriculture and Food Innovation</t>
+          <t>Sydney Institute of Agriculture, School of Life and Environmental Sciences, The University of Sydney, Australia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Plant pathology; Phytophthora; Molecular phylogenetics</t>
+          <t>Plant Pathology; Plant-Pathogen Interaction; Integrated Crop Management</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,22 +1205,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Peri Tobias</t>
+          <t>Prof. Andre Drenth</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Life Earth &amp; Environmental Sciences, The University of Sydney, Australia</t>
+          <t>Centre for Horticultural Science &amp; Professorial Research Fellow and Centre Director, Queensland Alliance for Agriculture and Food Innovation</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Plant biology; Plant molecular response to pathogens;</t>
+          <t>Plant pathology; Phytophthora; Molecular phylogenetics</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1242,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Jacob Downs</t>
+          <t>Dr. Peri Tobias</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,7 +1257,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Molecular biology and genetics of plants and fungi</t>
+          <t>Plant biology; Plant molecular response to pathogens;</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,22 +1279,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Anne Besantya Carroline, S.P.</t>
+          <t>Dr. Jacob Downs</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Life Earth &amp; Environmental Sciences, The University of Sydney, Australia</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Cacao Pod Rot Disease</t>
+          <t>Molecular biology and genetics of plants and fungi</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1320,12 +1316,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>St. Nurhaliza, S.P.</t>
+          <t>Anne Besantya Carroline, S.P.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1335,7 +1331,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Graduate Student</t>
+          <t>Cacao Pod Rot Disease</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1357,12 +1353,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Satriani Gassing, S.P.</t>
+          <t>St. Nurhaliza, S.P.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Patriani, A.Md., S.P.</t>
+          <t>Satriani Gassing, S.P.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1431,12 +1427,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>A. Aulia Nursyahbani</t>
+          <t>Patriani, A.Md., S.P.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1446,7 +1442,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Undergraduate Student</t>
+          <t>Graduate Student</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1468,12 +1464,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Ayu Agustina S.</t>
+          <t>A. Aulia Nursyahbani</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1505,12 +1501,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Amanda Aveline Kezia Manurun</t>
+          <t>Ayu Agustina S.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1542,12 +1538,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Muh. Wirahadi Kusuma</t>
+          <t>Amanda Aveline Kezia Manurun</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1577,10 +1573,26 @@
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Muh. Wirahadi Kusuma</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Undergraduate Student</t>
+        </is>
+      </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
@@ -1588,7 +1600,11 @@
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1777,15 +1793,32 @@
       <c r="L34" s="12" t="n"/>
       <c r="M34" s="12" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_p-rg.xlsx
+++ b/forms/trg/Formulir_TRG_p-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
